--- a/exercise/Quiz/Quiz Excel 21.xlsx
+++ b/exercise/Quiz/Quiz Excel 21.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Quiz\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7065" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SOAL1" sheetId="2" r:id="rId1"/>
@@ -113,7 +118,7 @@
     <definedName name="Z_9A428CE1_B4D9_11D0_A8AA_0000C071AEE7_.wvu.Rows" localSheetId="1" hidden="1">[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!$A$98:$IV$272</definedName>
     <definedName name="Z_9A428CE1_B4D9_11D0_A8AA_0000C071AEE7_.wvu.Rows" hidden="1">[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!$A$98:$IV$272</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -507,17 +512,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="&quot;Rp.&quot;* #,##0"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="&quot;Rp.&quot;* #,##0"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="&quot;Rp&quot;#,##0"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,158 +564,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -749,194 +608,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1056,409 +729,140 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="52">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="47">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="51" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="51" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="5" borderId="8" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="51" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="51" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="47"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="47" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="47" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="47" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="47" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="47" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="47" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="47" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="47" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="47" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="47" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="47" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="5" xfId="50" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="47" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="47" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="50" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="47" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="50" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="47" applyBorder="1"/>
-    <xf numFmtId="178" fontId="1" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="1" fillId="5" borderId="8" xfId="47" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="6">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0] 2" xfId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
-    <cellStyle name="Normal_soal untuk intermediate 1" xfId="47"/>
-    <cellStyle name="40% - Accent6" xfId="48" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="49" builtinId="52"/>
-    <cellStyle name="Comma [0] 2" xfId="50"/>
-    <cellStyle name="Normal_LATIHAN LOOKUP DAN IF" xfId="51"/>
+    <cellStyle name="Normal_LATIHAN LOOKUP DAN IF" xfId="5"/>
+    <cellStyle name="Normal_soal untuk intermediate 1" xfId="3"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="COST"/>
@@ -1489,7 +893,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="SOAL1"/>
@@ -1767,552 +1171,552 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6" style="25" customWidth="1"/>
-    <col min="2" max="2" width="12.7090909090909" style="25" customWidth="1"/>
-    <col min="3" max="4" width="10.7090909090909" style="25" customWidth="1"/>
-    <col min="5" max="5" width="15.5727272727273" style="25" customWidth="1"/>
-    <col min="6" max="6" width="9.13636363636364" style="25"/>
-    <col min="7" max="7" width="10.1363636363636" style="25" customWidth="1"/>
-    <col min="8" max="8" width="9.13636363636364" style="25"/>
-    <col min="9" max="9" width="20.5727272727273" style="25" customWidth="1"/>
-    <col min="10" max="10" width="17.1363636363636" style="25" customWidth="1"/>
-    <col min="11" max="11" width="16.4272727272727" style="25" customWidth="1"/>
-    <col min="12" max="12" width="13.7090909090909" style="25" customWidth="1"/>
-    <col min="13" max="13" width="18.7090909090909" style="25" customWidth="1"/>
-    <col min="14" max="16384" width="9.13636363636364" style="25"/>
+    <col min="1" max="1" width="6" style="23" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="23" customWidth="1"/>
+    <col min="3" max="4" width="10.7109375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="23"/>
+    <col min="7" max="7" width="10.140625" style="23" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="23"/>
+    <col min="9" max="9" width="20.5703125" style="23" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" style="23" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" style="23" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" style="23" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" style="23" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" spans="1:1">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:13" ht="15.75">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15.5" spans="1:13">
-      <c r="A3" s="27" t="s">
+    <row r="3" spans="1:13" ht="15.75">
+      <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-    </row>
-    <row r="4" ht="15.5" spans="1:13">
-      <c r="A4" s="27" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+    </row>
+    <row r="4" spans="1:13" ht="15.75">
+      <c r="A4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-    </row>
-    <row r="6" ht="25" spans="1:13">
-      <c r="A6" s="28" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+    </row>
+    <row r="6" spans="1:13" ht="25.5">
+      <c r="A6" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="28" t="s">
+      <c r="K6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="L6" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="28" t="s">
+      <c r="M6" s="25" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="29">
+      <c r="A7" s="26">
         <v>1</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="29">
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="26">
         <v>4</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="29">
+      <c r="A8" s="26">
         <v>2</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="29">
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="26">
         <v>0</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="29">
+      <c r="A9" s="26">
         <v>3</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="29">
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="26">
         <v>2</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="29">
+      <c r="A10" s="26">
         <v>4</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="29">
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="26">
         <v>0</v>
       </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="29">
+      <c r="A11" s="26">
         <v>5</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="29">
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="26">
         <v>1</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="29">
+      <c r="A12" s="26">
         <v>6</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="29">
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="26">
         <v>2</v>
       </c>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="29">
+      <c r="A13" s="26">
         <v>7</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="29">
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="26">
         <v>0</v>
       </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="29">
+      <c r="A14" s="26">
         <v>8</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="29">
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="26">
         <v>3</v>
       </c>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="29">
+      <c r="A15" s="26">
         <v>9</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="29">
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="26">
         <v>0</v>
       </c>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="29">
+      <c r="A16" s="26">
         <v>10</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="29">
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="26">
         <v>5</v>
       </c>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="46"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="43"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="46"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="43"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="46"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="43"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="46"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="25" t="s">
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="43"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="23" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="25" t="s">
+    <row r="23" spans="1:13">
+      <c r="A23" s="23" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="25" t="s">
+    <row r="24" spans="1:13">
+      <c r="A24" s="23" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="25" t="s">
+    <row r="25" spans="1:13">
+      <c r="A25" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="25" t="s">
+    <row r="26" spans="1:13">
+      <c r="A26" s="23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="25" t="s">
+    <row r="27" spans="1:13">
+      <c r="A27" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="25" t="s">
+    <row r="28" spans="1:13">
+      <c r="A28" s="23" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="25" t="s">
+    <row r="29" spans="1:13">
+      <c r="A29" s="23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="25" t="s">
+    <row r="30" spans="1:13">
+      <c r="A30" s="23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="25" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="25" t="s">
+    <row r="32" spans="1:13">
+      <c r="A32" s="23" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="34" t="s">
+      <c r="A35" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="34" t="s">
+      <c r="B35" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="34" t="s">
+      <c r="E35" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="36" t="s">
+      <c r="A36" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="36" t="s">
+      <c r="B36" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="34">
         <v>1</v>
       </c>
-      <c r="E36" s="38">
+      <c r="E36" s="35">
         <v>8000000</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="39" t="s">
+      <c r="A37" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="40">
+      <c r="D37" s="37">
         <v>2</v>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="38">
         <v>6000000</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="39" t="s">
+      <c r="A38" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="40">
+      <c r="D38" s="37">
         <v>3</v>
       </c>
-      <c r="E38" s="41">
+      <c r="E38" s="38">
         <v>4500000</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="39" t="s">
+      <c r="A39" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="40">
+      <c r="D39" s="37">
         <v>4</v>
       </c>
-      <c r="E39" s="41">
+      <c r="E39" s="38">
         <v>3000000</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="39" t="s">
+      <c r="A40" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="B40" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D40" s="42">
+      <c r="D40" s="39">
         <v>5</v>
       </c>
-      <c r="E40" s="43">
+      <c r="E40" s="40">
         <v>1500000</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="44" t="s">
+    <row r="41" spans="1:5">
+      <c r="A41" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="44" t="s">
+      <c r="B41" s="41" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2322,31 +1726,31 @@
     <mergeCell ref="A4:M4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.31496062992126" right="0.354330708661417" top="0.511811023622047" bottom="0.984251968503937" header="0.354330708661417" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="97" orientation="landscape"/>
+  <pageMargins left="0.31496062992126" right="0.35433070866141703" top="0.511811023622047" bottom="0.98425196850393704" header="0.35433070866141703" footer="0.511811023622047"/>
+  <pageSetup scale="97" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="9.13636363636364" style="1"/>
-    <col min="3" max="3" width="13.1363636363636" style="1" customWidth="1"/>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="13.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.8545454545455" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.2818181818182" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="1" customWidth="1"/>
-    <col min="8" max="9" width="14.2818181818182" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.8545454545455" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.4272727272727" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.13636363636364" style="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="50" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:11">
+    <row r="1" spans="1:11" ht="15">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2355,11 +1759,11 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" ht="13.5" spans="1:11">
+    <row r="2" spans="1:11" ht="15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2368,11 +1772,11 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="I2" s="46"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" ht="19" spans="1:11">
+    <row r="3" spans="1:11" ht="18.75">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -2383,11 +1787,11 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="I3" s="46"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" ht="13.5" spans="1:11">
+    <row r="4" spans="1:11" ht="15">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2396,11 +1800,11 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="I4" s="46"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" ht="27" spans="1:11">
+    <row r="5" spans="1:11" ht="30">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
         <v>65</v>
@@ -2423,17 +1827,17 @@
       <c r="H5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="47" t="s">
         <v>72</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" ht="13.5" spans="1:11">
+    <row r="6" spans="1:11" ht="15">
       <c r="A6" s="9"/>
       <c r="B6" s="10">
         <v>1</v>
@@ -2444,15 +1848,27 @@
       <c r="D6" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="20"/>
+      <c r="E6" s="12" t="str">
+        <f>VLOOKUP(LEFT(D6,2),$B$19:$E$24,2,FALSE)</f>
+        <v>Lorena</v>
+      </c>
+      <c r="F6" s="12" t="str">
+        <f>VLOOKUP(LEFT(D6,2),$B$19:$E$24,3,FALSE)</f>
+        <v>Jakarta-Denpasar</v>
+      </c>
+      <c r="G6" s="12" t="str">
+        <f>VLOOKUP(MID(D6,4,2),$G$19:$I$23,2,FALSE)</f>
+        <v>Super Eksekutif</v>
+      </c>
+      <c r="H6" s="13">
+        <f>VLOOKUP(LEFT(D6,2),$B$19:$E$24,4,FALSE)</f>
+        <v>220000</v>
+      </c>
+      <c r="I6" s="51"/>
+      <c r="J6" s="19"/>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" ht="13.5" spans="1:11">
+    <row r="7" spans="1:11" ht="15">
       <c r="A7" s="9"/>
       <c r="B7" s="10">
         <v>2</v>
@@ -2463,15 +1879,27 @@
       <c r="D7" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="20"/>
+      <c r="E7" s="12" t="str">
+        <f t="shared" ref="E7:E17" si="0">VLOOKUP(LEFT(D7,2),$B$19:$E$24,2,FALSE)</f>
+        <v>Lorena</v>
+      </c>
+      <c r="F7" s="12" t="str">
+        <f t="shared" ref="F7:F17" si="1">VLOOKUP(LEFT(D7,2),$B$19:$E$24,3,FALSE)</f>
+        <v>Jakarta-Denpasar</v>
+      </c>
+      <c r="G7" s="12" t="str">
+        <f t="shared" ref="G7:G17" si="2">VLOOKUP(MID(D7,4,2),$G$19:$I$23,2,FALSE)</f>
+        <v>Super Eksekutif</v>
+      </c>
+      <c r="H7" s="13">
+        <f t="shared" ref="H7:H17" si="3">VLOOKUP(LEFT(D7,2),$B$19:$E$24,4,FALSE)</f>
+        <v>220000</v>
+      </c>
+      <c r="I7" s="51"/>
+      <c r="J7" s="19"/>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" ht="13.5" spans="1:11">
+    <row r="8" spans="1:11" ht="15">
       <c r="A8" s="9"/>
       <c r="B8" s="10">
         <v>3</v>
@@ -2482,15 +1910,27 @@
       <c r="D8" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="20"/>
+      <c r="E8" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Setia Negara</v>
+      </c>
+      <c r="F8" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Semarang</v>
+      </c>
+      <c r="G8" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Bisnis</v>
+      </c>
+      <c r="H8" s="13">
+        <f t="shared" si="3"/>
+        <v>120000</v>
+      </c>
+      <c r="I8" s="51"/>
+      <c r="J8" s="19"/>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" ht="13.5" spans="1:11">
+    <row r="9" spans="1:11" ht="15">
       <c r="A9" s="9"/>
       <c r="B9" s="10">
         <v>4</v>
@@ -2501,15 +1941,27 @@
       <c r="D9" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="20"/>
+      <c r="E9" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Luragung Jaya</v>
+      </c>
+      <c r="F9" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Cirebon</v>
+      </c>
+      <c r="G9" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Ekonomi</v>
+      </c>
+      <c r="H9" s="13">
+        <f t="shared" si="3"/>
+        <v>40000</v>
+      </c>
+      <c r="I9" s="51"/>
+      <c r="J9" s="19"/>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" ht="13.5" spans="1:11">
+    <row r="10" spans="1:11" ht="15">
       <c r="A10" s="9"/>
       <c r="B10" s="10">
         <v>5</v>
@@ -2520,15 +1972,27 @@
       <c r="D10" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="20"/>
+      <c r="E10" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Sahabat</v>
+      </c>
+      <c r="F10" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Kuningan</v>
+      </c>
+      <c r="G10" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Super Eksekutif</v>
+      </c>
+      <c r="H10" s="13">
+        <f t="shared" si="3"/>
+        <v>60000</v>
+      </c>
+      <c r="I10" s="51"/>
+      <c r="J10" s="19"/>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" ht="13.5" spans="1:11">
+    <row r="11" spans="1:11" ht="15">
       <c r="A11" s="9"/>
       <c r="B11" s="10">
         <v>6</v>
@@ -2539,15 +2003,27 @@
       <c r="D11" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="20"/>
+      <c r="E11" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Sami Jaya</v>
+      </c>
+      <c r="F11" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Surabaya</v>
+      </c>
+      <c r="G11" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Eksekutif</v>
+      </c>
+      <c r="H11" s="13">
+        <f t="shared" si="3"/>
+        <v>190000</v>
+      </c>
+      <c r="I11" s="51"/>
+      <c r="J11" s="19"/>
       <c r="K11" s="10"/>
     </row>
-    <row r="12" ht="13.5" spans="1:11">
+    <row r="12" spans="1:11" ht="15">
       <c r="A12" s="9"/>
       <c r="B12" s="10">
         <v>7</v>
@@ -2558,15 +2034,27 @@
       <c r="D12" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="20"/>
+      <c r="E12" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Setia Negara</v>
+      </c>
+      <c r="F12" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Semarang</v>
+      </c>
+      <c r="G12" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Bisnis</v>
+      </c>
+      <c r="H12" s="13">
+        <f t="shared" si="3"/>
+        <v>120000</v>
+      </c>
+      <c r="I12" s="51"/>
+      <c r="J12" s="19"/>
       <c r="K12" s="10"/>
     </row>
-    <row r="13" ht="13.5" spans="1:11">
+    <row r="13" spans="1:11" ht="15">
       <c r="A13" s="9"/>
       <c r="B13" s="10">
         <v>8</v>
@@ -2577,15 +2065,27 @@
       <c r="D13" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="20"/>
+      <c r="E13" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Luragung Jaya</v>
+      </c>
+      <c r="F13" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Cirebon</v>
+      </c>
+      <c r="G13" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Ekonomi</v>
+      </c>
+      <c r="H13" s="13">
+        <f t="shared" si="3"/>
+        <v>40000</v>
+      </c>
+      <c r="I13" s="51"/>
+      <c r="J13" s="19"/>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" ht="13.5" spans="1:11">
+    <row r="14" spans="1:11" ht="15">
       <c r="A14" s="9"/>
       <c r="B14" s="10">
         <v>9</v>
@@ -2596,15 +2096,27 @@
       <c r="D14" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="20"/>
+      <c r="E14" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Lorena</v>
+      </c>
+      <c r="F14" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Denpasar</v>
+      </c>
+      <c r="G14" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Super Eksekutif</v>
+      </c>
+      <c r="H14" s="13">
+        <f t="shared" si="3"/>
+        <v>220000</v>
+      </c>
+      <c r="I14" s="51"/>
+      <c r="J14" s="19"/>
       <c r="K14" s="10"/>
     </row>
-    <row r="15" ht="13.5" spans="1:11">
+    <row r="15" spans="1:11" ht="15">
       <c r="A15" s="9"/>
       <c r="B15" s="10">
         <v>10</v>
@@ -2615,15 +2127,27 @@
       <c r="D15" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="20"/>
+      <c r="E15" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Setia Negara</v>
+      </c>
+      <c r="F15" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Semarang</v>
+      </c>
+      <c r="G15" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Eksekutif</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="3"/>
+        <v>120000</v>
+      </c>
+      <c r="I15" s="51"/>
+      <c r="J15" s="19"/>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" ht="13.5" spans="1:11">
+    <row r="16" spans="1:11" ht="15">
       <c r="A16" s="9"/>
       <c r="B16" s="10">
         <v>11</v>
@@ -2634,15 +2158,27 @@
       <c r="D16" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="20"/>
+      <c r="E16" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Luragung Jaya</v>
+      </c>
+      <c r="F16" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Cirebon</v>
+      </c>
+      <c r="G16" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Ekonomi</v>
+      </c>
+      <c r="H16" s="13">
+        <f t="shared" si="3"/>
+        <v>40000</v>
+      </c>
+      <c r="I16" s="51"/>
+      <c r="J16" s="19"/>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" ht="13.5" spans="1:11">
+    <row r="17" spans="1:14" ht="15">
       <c r="A17" s="9"/>
       <c r="B17" s="10">
         <v>12</v>
@@ -2653,15 +2189,27 @@
       <c r="D17" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="20"/>
+      <c r="E17" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Sahabat</v>
+      </c>
+      <c r="F17" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>Jakarta-Kuningan</v>
+      </c>
+      <c r="G17" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Super Eksekutif</v>
+      </c>
+      <c r="H17" s="13">
+        <f t="shared" si="3"/>
+        <v>60000</v>
+      </c>
+      <c r="I17" s="51"/>
+      <c r="J17" s="19"/>
       <c r="K17" s="10"/>
     </row>
-    <row r="18" ht="13.5" spans="1:11">
+    <row r="18" spans="1:14" ht="15">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2670,11 +2218,11 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="I18" s="46"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" ht="13.5" spans="1:11">
+    <row r="19" spans="1:14" ht="30">
       <c r="A19" s="9"/>
       <c r="B19" s="6" t="s">
         <v>67</v>
@@ -2695,13 +2243,13 @@
       <c r="H19" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I19" s="19" t="s">
+      <c r="I19" s="48" t="s">
         <v>72</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" ht="13.5" spans="1:14">
+    <row r="20" spans="1:14" ht="15">
       <c r="A20" s="3"/>
       <c r="B20" s="15" t="s">
         <v>97</v>
@@ -2722,16 +2270,16 @@
       <c r="H20" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="49">
         <v>0.25</v>
       </c>
       <c r="J20" s="3"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="23"/>
-    </row>
-    <row r="21" ht="13.5" spans="1:14">
+      <c r="K20" s="20"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="21"/>
+    </row>
+    <row r="21" spans="1:14" ht="15">
       <c r="A21" s="3"/>
       <c r="B21" s="15" t="s">
         <v>102</v>
@@ -2752,16 +2300,16 @@
       <c r="H21" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="49">
         <v>0</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="23"/>
-    </row>
-    <row r="22" ht="13.5" spans="1:14">
+      <c r="K21" s="20"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="21"/>
+    </row>
+    <row r="22" spans="1:14" ht="15">
       <c r="A22" s="3"/>
       <c r="B22" s="15" t="s">
         <v>107</v>
@@ -2782,16 +2330,16 @@
       <c r="H22" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="49">
         <v>0.5</v>
       </c>
       <c r="J22" s="3"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="23"/>
-    </row>
-    <row r="23" ht="13.5" spans="1:11">
+      <c r="K22" s="20"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="21"/>
+    </row>
+    <row r="23" spans="1:14" ht="15">
       <c r="A23" s="3"/>
       <c r="B23" s="15" t="s">
         <v>112</v>
@@ -2812,13 +2360,13 @@
       <c r="H23" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="49">
         <v>0.75</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" ht="13.5" spans="1:11">
+    <row r="24" spans="1:14" ht="15">
       <c r="A24" s="3"/>
       <c r="B24" s="15" t="s">
         <v>117</v>
@@ -2835,11 +2383,11 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="I24" s="46"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" ht="13.5" spans="1:11">
+    <row r="25" spans="1:14" ht="15">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2848,46 +2396,46 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="I25" s="46"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
     </row>
-    <row r="26" ht="13.5" spans="2:2">
+    <row r="26" spans="1:14" ht="15">
       <c r="B26" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="27" ht="13.5" spans="2:2">
+    <row r="27" spans="1:14" ht="15">
       <c r="B27" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" ht="13.5" spans="2:2">
+    <row r="28" spans="1:14" ht="15">
       <c r="B28" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="29" ht="13.5" spans="2:2">
+    <row r="29" spans="1:14" ht="15">
       <c r="B29" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" ht="13.5" spans="2:2">
+    <row r="30" spans="1:14" ht="15">
       <c r="B30" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" ht="13.5" spans="2:2">
+    <row r="31" spans="1:14" ht="15">
       <c r="B31" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" ht="13.5" spans="2:2">
+    <row r="32" spans="1:14" ht="15">
       <c r="B32" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" ht="13.5" spans="2:2">
+    <row r="33" spans="2:2" ht="15">
       <c r="B33" s="3" t="s">
         <v>127</v>
       </c>

--- a/exercise/Quiz/Quiz Excel 21.xlsx
+++ b/exercise/Quiz/Quiz Excel 21.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Quiz\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7065" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SOAL1" sheetId="2" r:id="rId1"/>
@@ -118,7 +113,7 @@
     <definedName name="Z_9A428CE1_B4D9_11D0_A8AA_0000C071AEE7_.wvu.Rows" localSheetId="1" hidden="1">[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!$A$98:$IV$272</definedName>
     <definedName name="Z_9A428CE1_B4D9_11D0_A8AA_0000C071AEE7_.wvu.Rows" hidden="1">[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!#REF!,[1]MASTER!$A$98:$IV$272</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -512,15 +507,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="&quot;Rp.&quot;* #,##0"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="172" formatCode="&quot;Rp&quot;#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="&quot;Rp.&quot;* #,##0"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,14 +561,158 @@
       <charset val="134"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -608,8 +749,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -729,140 +1056,409 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="51" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="51" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="51" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="51" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="47"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="47" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="47" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="47" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="47" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="47" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="47" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="47" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="47" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="47" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="47" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="47" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="5" xfId="50" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="47" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="47" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="50" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="47" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="3" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="5" borderId="8" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="50" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="47" applyBorder="1"/>
+    <xf numFmtId="178" fontId="1" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="1" fillId="5" borderId="8" xfId="47" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0] 2" xfId="4"/>
+  <cellStyles count="52">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_LATIHAN LOOKUP DAN IF" xfId="5"/>
-    <cellStyle name="Normal_soal untuk intermediate 1" xfId="3"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Currency" xfId="5" builtinId="4"/>
+    <cellStyle name="Percent" xfId="6" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
+    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
+    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
+    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
+    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
+    <cellStyle name="Note" xfId="12" builtinId="10"/>
+    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="Title" xfId="16" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
+    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
+    <cellStyle name="Input" xfId="21" builtinId="20"/>
+    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
+    <cellStyle name="Good" xfId="23" builtinId="26"/>
+    <cellStyle name="Output" xfId="24" builtinId="21"/>
+    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
+    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
+    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
+    <cellStyle name="Total" xfId="28" builtinId="25"/>
+    <cellStyle name="Bad" xfId="29" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
+    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
+    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
+    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
+    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
+    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
+    <cellStyle name="Normal_soal untuk intermediate 1" xfId="47"/>
+    <cellStyle name="40% - Accent6" xfId="48" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="49" builtinId="52"/>
+    <cellStyle name="Comma [0] 2" xfId="50"/>
+    <cellStyle name="Normal_LATIHAN LOOKUP DAN IF" xfId="51"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="COST"/>
@@ -893,7 +1489,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="SOAL1"/>
@@ -1171,552 +1767,552 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="6" style="23" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="23" customWidth="1"/>
-    <col min="3" max="4" width="10.7109375" style="23" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="23"/>
-    <col min="7" max="7" width="10.140625" style="23" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="23"/>
-    <col min="9" max="9" width="20.5703125" style="23" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" style="23" customWidth="1"/>
-    <col min="11" max="11" width="16.42578125" style="23" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" style="23" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" style="23" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="1" width="6" style="25" customWidth="1"/>
+    <col min="2" max="2" width="12.7090909090909" style="25" customWidth="1"/>
+    <col min="3" max="4" width="10.7090909090909" style="25" customWidth="1"/>
+    <col min="5" max="5" width="15.5727272727273" style="25" customWidth="1"/>
+    <col min="6" max="6" width="9.13636363636364" style="25"/>
+    <col min="7" max="7" width="10.1363636363636" style="25" customWidth="1"/>
+    <col min="8" max="8" width="9.13636363636364" style="25"/>
+    <col min="9" max="9" width="20.5727272727273" style="25" customWidth="1"/>
+    <col min="10" max="10" width="17.1363636363636" style="25" customWidth="1"/>
+    <col min="11" max="11" width="16.4272727272727" style="25" customWidth="1"/>
+    <col min="12" max="12" width="13.7090909090909" style="25" customWidth="1"/>
+    <col min="13" max="13" width="18.7090909090909" style="25" customWidth="1"/>
+    <col min="14" max="16384" width="9.13636363636364" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75">
-      <c r="A1" s="24" t="s">
+    <row r="1" ht="15.5" spans="1:1">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75">
-      <c r="A3" s="44" t="s">
+    <row r="3" ht="15.5" spans="1:13">
+      <c r="A3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.75">
-      <c r="A4" s="44" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+    </row>
+    <row r="4" ht="15.5" spans="1:13">
+      <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-    </row>
-    <row r="6" spans="1:13" ht="25.5">
-      <c r="A6" s="25" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+    </row>
+    <row r="6" ht="25" spans="1:13">
+      <c r="A6" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="25" t="s">
+      <c r="K6" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M6" s="28" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="26">
+      <c r="A7" s="29">
         <v>1</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="26">
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="29">
         <v>4</v>
       </c>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="26">
+      <c r="A8" s="29">
         <v>2</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="26">
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="29">
         <v>0</v>
       </c>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="26">
+      <c r="A9" s="29">
         <v>3</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="26">
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="29">
         <v>2</v>
       </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="26">
+      <c r="A10" s="29">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="26">
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="29">
         <v>0</v>
       </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="26">
+      <c r="A11" s="29">
         <v>5</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="26">
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="29">
         <v>1</v>
       </c>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="26">
+      <c r="A12" s="29">
         <v>6</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="26">
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="29">
         <v>2</v>
       </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="26">
+      <c r="A13" s="29">
         <v>7</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="26">
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="29">
         <v>0</v>
       </c>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="26">
+      <c r="A14" s="29">
         <v>8</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="26">
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="29">
         <v>3</v>
       </c>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="45"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="26">
+      <c r="A15" s="29">
         <v>9</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="26">
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="29">
         <v>0</v>
       </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="26">
+      <c r="A16" s="29">
         <v>10</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="26">
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="29">
         <v>5</v>
       </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="43"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="46"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="43"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="46"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="43"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="46"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="43"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="23" t="s">
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="46"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="23" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="25" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="23" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" s="25" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="23" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="25" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="23" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" s="25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="23" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" s="25" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="23" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" s="25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="23" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="23" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" s="25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="23" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" s="25" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="23" t="s">
+    <row r="32" spans="1:1">
+      <c r="A32" s="25" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="31" t="s">
+      <c r="E35" s="34" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="33" t="s">
+      <c r="A36" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="33" t="s">
+      <c r="B36" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="37">
         <v>1</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="38">
         <v>8000000</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="36" t="s">
+      <c r="B37" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="37">
+      <c r="D37" s="40">
         <v>2</v>
       </c>
-      <c r="E37" s="38">
+      <c r="E37" s="41">
         <v>6000000</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="36" t="s">
+      <c r="A38" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="36" t="s">
+      <c r="B38" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="37">
+      <c r="D38" s="40">
         <v>3</v>
       </c>
-      <c r="E38" s="38">
+      <c r="E38" s="41">
         <v>4500000</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B39" s="36" t="s">
+      <c r="B39" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="37">
+      <c r="D39" s="40">
         <v>4</v>
       </c>
-      <c r="E39" s="38">
+      <c r="E39" s="41">
         <v>3000000</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="36" t="s">
+      <c r="A40" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="D40" s="39">
+      <c r="D40" s="42">
         <v>5</v>
       </c>
-      <c r="E40" s="40">
+      <c r="E40" s="43">
         <v>1500000</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="41" t="s">
+    <row r="41" spans="1:2">
+      <c r="A41" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="44" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1726,31 +2322,31 @@
     <mergeCell ref="A4:M4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.31496062992126" right="0.35433070866141703" top="0.511811023622047" bottom="0.98425196850393704" header="0.35433070866141703" footer="0.511811023622047"/>
-  <pageSetup scale="97" orientation="landscape"/>
+  <pageMargins left="0.31496062992126" right="0.354330708661417" top="0.511811023622047" bottom="0.984251968503937" header="0.354330708661417" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="97" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="13.140625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="9.13636363636364" style="1"/>
+    <col min="3" max="3" width="13.1363636363636" style="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.8545454545455" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.2818181818182" style="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="50" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="9" width="14.2818181818182" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.8545454545455" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.4272727272727" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.13636363636364" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15">
+    <row r="1" ht="13.5" spans="1:11">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1759,11 +2355,11 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="45"/>
+      <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="15">
+    <row r="2" ht="13.5" spans="1:11">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1772,11 +2368,11 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="46"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="18.75">
+    <row r="3" ht="19" spans="1:11">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>64</v>
@@ -1787,11 +2383,11 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="46"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" ht="15">
+    <row r="4" ht="13.5" spans="1:11">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1800,11 +2396,11 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="46"/>
+      <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="30">
+    <row r="5" ht="27" spans="1:11">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
         <v>65</v>
@@ -1827,17 +2423,17 @@
       <c r="H5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I5" s="47" t="s">
+      <c r="I5" s="18" t="s">
         <v>72</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15">
+    <row r="6" ht="13.5" spans="1:11">
       <c r="A6" s="9"/>
       <c r="B6" s="10">
         <v>1</v>
@@ -1848,27 +2444,15 @@
       <c r="D6" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="12" t="str">
-        <f>VLOOKUP(LEFT(D6,2),$B$19:$E$24,2,FALSE)</f>
-        <v>Lorena</v>
-      </c>
-      <c r="F6" s="12" t="str">
-        <f>VLOOKUP(LEFT(D6,2),$B$19:$E$24,3,FALSE)</f>
-        <v>Jakarta-Denpasar</v>
-      </c>
-      <c r="G6" s="12" t="str">
-        <f>VLOOKUP(MID(D6,4,2),$G$19:$I$23,2,FALSE)</f>
-        <v>Super Eksekutif</v>
-      </c>
-      <c r="H6" s="13">
-        <f>VLOOKUP(LEFT(D6,2),$B$19:$E$24,4,FALSE)</f>
-        <v>220000</v>
-      </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="19"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="20"/>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" spans="1:11" ht="15">
+    <row r="7" ht="13.5" spans="1:11">
       <c r="A7" s="9"/>
       <c r="B7" s="10">
         <v>2</v>
@@ -1879,27 +2463,15 @@
       <c r="D7" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="12" t="str">
-        <f t="shared" ref="E7:E17" si="0">VLOOKUP(LEFT(D7,2),$B$19:$E$24,2,FALSE)</f>
-        <v>Lorena</v>
-      </c>
-      <c r="F7" s="12" t="str">
-        <f t="shared" ref="F7:F17" si="1">VLOOKUP(LEFT(D7,2),$B$19:$E$24,3,FALSE)</f>
-        <v>Jakarta-Denpasar</v>
-      </c>
-      <c r="G7" s="12" t="str">
-        <f t="shared" ref="G7:G17" si="2">VLOOKUP(MID(D7,4,2),$G$19:$I$23,2,FALSE)</f>
-        <v>Super Eksekutif</v>
-      </c>
-      <c r="H7" s="13">
-        <f t="shared" ref="H7:H17" si="3">VLOOKUP(LEFT(D7,2),$B$19:$E$24,4,FALSE)</f>
-        <v>220000</v>
-      </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="19"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="20"/>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="1:11" ht="15">
+    <row r="8" ht="13.5" spans="1:11">
       <c r="A8" s="9"/>
       <c r="B8" s="10">
         <v>3</v>
@@ -1910,27 +2482,15 @@
       <c r="D8" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Setia Negara</v>
-      </c>
-      <c r="F8" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Semarang</v>
-      </c>
-      <c r="G8" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Bisnis</v>
-      </c>
-      <c r="H8" s="13">
-        <f t="shared" si="3"/>
-        <v>120000</v>
-      </c>
-      <c r="I8" s="51"/>
-      <c r="J8" s="19"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="20"/>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="1:11" ht="15">
+    <row r="9" ht="13.5" spans="1:11">
       <c r="A9" s="9"/>
       <c r="B9" s="10">
         <v>4</v>
@@ -1941,27 +2501,15 @@
       <c r="D9" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Luragung Jaya</v>
-      </c>
-      <c r="F9" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Cirebon</v>
-      </c>
-      <c r="G9" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Ekonomi</v>
-      </c>
-      <c r="H9" s="13">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="I9" s="51"/>
-      <c r="J9" s="19"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="20"/>
       <c r="K9" s="10"/>
     </row>
-    <row r="10" spans="1:11" ht="15">
+    <row r="10" ht="13.5" spans="1:11">
       <c r="A10" s="9"/>
       <c r="B10" s="10">
         <v>5</v>
@@ -1972,27 +2520,15 @@
       <c r="D10" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Sahabat</v>
-      </c>
-      <c r="F10" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Kuningan</v>
-      </c>
-      <c r="G10" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Super Eksekutif</v>
-      </c>
-      <c r="H10" s="13">
-        <f t="shared" si="3"/>
-        <v>60000</v>
-      </c>
-      <c r="I10" s="51"/>
-      <c r="J10" s="19"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="20"/>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" spans="1:11" ht="15">
+    <row r="11" ht="13.5" spans="1:11">
       <c r="A11" s="9"/>
       <c r="B11" s="10">
         <v>6</v>
@@ -2003,27 +2539,15 @@
       <c r="D11" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Sami Jaya</v>
-      </c>
-      <c r="F11" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Surabaya</v>
-      </c>
-      <c r="G11" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Eksekutif</v>
-      </c>
-      <c r="H11" s="13">
-        <f t="shared" si="3"/>
-        <v>190000</v>
-      </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="19"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="20"/>
       <c r="K11" s="10"/>
     </row>
-    <row r="12" spans="1:11" ht="15">
+    <row r="12" ht="13.5" spans="1:11">
       <c r="A12" s="9"/>
       <c r="B12" s="10">
         <v>7</v>
@@ -2034,27 +2558,15 @@
       <c r="D12" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Setia Negara</v>
-      </c>
-      <c r="F12" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Semarang</v>
-      </c>
-      <c r="G12" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Bisnis</v>
-      </c>
-      <c r="H12" s="13">
-        <f t="shared" si="3"/>
-        <v>120000</v>
-      </c>
-      <c r="I12" s="51"/>
-      <c r="J12" s="19"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="20"/>
       <c r="K12" s="10"/>
     </row>
-    <row r="13" spans="1:11" ht="15">
+    <row r="13" ht="13.5" spans="1:11">
       <c r="A13" s="9"/>
       <c r="B13" s="10">
         <v>8</v>
@@ -2065,27 +2577,15 @@
       <c r="D13" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Luragung Jaya</v>
-      </c>
-      <c r="F13" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Cirebon</v>
-      </c>
-      <c r="G13" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Ekonomi</v>
-      </c>
-      <c r="H13" s="13">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="I13" s="51"/>
-      <c r="J13" s="19"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="20"/>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" spans="1:11" ht="15">
+    <row r="14" ht="13.5" spans="1:11">
       <c r="A14" s="9"/>
       <c r="B14" s="10">
         <v>9</v>
@@ -2096,27 +2596,15 @@
       <c r="D14" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Lorena</v>
-      </c>
-      <c r="F14" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Denpasar</v>
-      </c>
-      <c r="G14" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Super Eksekutif</v>
-      </c>
-      <c r="H14" s="13">
-        <f t="shared" si="3"/>
-        <v>220000</v>
-      </c>
-      <c r="I14" s="51"/>
-      <c r="J14" s="19"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="20"/>
       <c r="K14" s="10"/>
     </row>
-    <row r="15" spans="1:11" ht="15">
+    <row r="15" ht="13.5" spans="1:11">
       <c r="A15" s="9"/>
       <c r="B15" s="10">
         <v>10</v>
@@ -2127,27 +2615,15 @@
       <c r="D15" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Setia Negara</v>
-      </c>
-      <c r="F15" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Semarang</v>
-      </c>
-      <c r="G15" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Eksekutif</v>
-      </c>
-      <c r="H15" s="13">
-        <f t="shared" si="3"/>
-        <v>120000</v>
-      </c>
-      <c r="I15" s="51"/>
-      <c r="J15" s="19"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="20"/>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="1:11" ht="15">
+    <row r="16" ht="13.5" spans="1:11">
       <c r="A16" s="9"/>
       <c r="B16" s="10">
         <v>11</v>
@@ -2158,27 +2634,15 @@
       <c r="D16" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Luragung Jaya</v>
-      </c>
-      <c r="F16" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Cirebon</v>
-      </c>
-      <c r="G16" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Ekonomi</v>
-      </c>
-      <c r="H16" s="13">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="19"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="20"/>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:14" ht="15">
+    <row r="17" ht="13.5" spans="1:11">
       <c r="A17" s="9"/>
       <c r="B17" s="10">
         <v>12</v>
@@ -2189,27 +2653,15 @@
       <c r="D17" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>Sahabat</v>
-      </c>
-      <c r="F17" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v>Jakarta-Kuningan</v>
-      </c>
-      <c r="G17" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>Super Eksekutif</v>
-      </c>
-      <c r="H17" s="13">
-        <f t="shared" si="3"/>
-        <v>60000</v>
-      </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="19"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="20"/>
       <c r="K17" s="10"/>
     </row>
-    <row r="18" spans="1:14" ht="15">
+    <row r="18" ht="13.5" spans="1:11">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2218,11 +2670,11 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="46"/>
+      <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="1:14" ht="30">
+    <row r="19" ht="13.5" spans="1:11">
       <c r="A19" s="9"/>
       <c r="B19" s="6" t="s">
         <v>67</v>
@@ -2243,13 +2695,13 @@
       <c r="H19" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I19" s="48" t="s">
+      <c r="I19" s="19" t="s">
         <v>72</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="1:14" ht="15">
+    <row r="20" ht="13.5" spans="1:14">
       <c r="A20" s="3"/>
       <c r="B20" s="15" t="s">
         <v>97</v>
@@ -2270,16 +2722,16 @@
       <c r="H20" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="I20" s="49">
+      <c r="I20" s="21">
         <v>0.25</v>
       </c>
       <c r="J20" s="3"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="21"/>
-    </row>
-    <row r="21" spans="1:14" ht="15">
+      <c r="K20" s="22"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="23"/>
+    </row>
+    <row r="21" ht="13.5" spans="1:14">
       <c r="A21" s="3"/>
       <c r="B21" s="15" t="s">
         <v>102</v>
@@ -2300,16 +2752,16 @@
       <c r="H21" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="I21" s="49">
+      <c r="I21" s="21">
         <v>0</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="21"/>
-    </row>
-    <row r="22" spans="1:14" ht="15">
+      <c r="K21" s="22"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="23"/>
+    </row>
+    <row r="22" ht="13.5" spans="1:14">
       <c r="A22" s="3"/>
       <c r="B22" s="15" t="s">
         <v>107</v>
@@ -2330,16 +2782,16 @@
       <c r="H22" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="I22" s="49">
+      <c r="I22" s="21">
         <v>0.5</v>
       </c>
       <c r="J22" s="3"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="21"/>
-    </row>
-    <row r="23" spans="1:14" ht="15">
+      <c r="K22" s="22"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="23"/>
+    </row>
+    <row r="23" ht="13.5" spans="1:11">
       <c r="A23" s="3"/>
       <c r="B23" s="15" t="s">
         <v>112</v>
@@ -2360,13 +2812,13 @@
       <c r="H23" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="I23" s="49">
+      <c r="I23" s="21">
         <v>0.75</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:14" ht="15">
+    <row r="24" ht="13.5" spans="1:11">
       <c r="A24" s="3"/>
       <c r="B24" s="15" t="s">
         <v>117</v>
@@ -2383,11 +2835,11 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="46"/>
+      <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:14" ht="15">
+    <row r="25" ht="13.5" spans="1:11">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2396,46 +2848,46 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="46"/>
+      <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
     </row>
-    <row r="26" spans="1:14" ht="15">
+    <row r="26" ht="13.5" spans="2:2">
       <c r="B26" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15">
+    <row r="27" ht="13.5" spans="2:2">
       <c r="B27" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15">
+    <row r="28" ht="13.5" spans="2:2">
       <c r="B28" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15">
+    <row r="29" ht="13.5" spans="2:2">
       <c r="B29" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15">
+    <row r="30" ht="13.5" spans="2:2">
       <c r="B30" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15">
+    <row r="31" ht="13.5" spans="2:2">
       <c r="B31" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15">
+    <row r="32" ht="13.5" spans="2:2">
       <c r="B32" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="15">
+    <row r="33" ht="13.5" spans="2:2">
       <c r="B33" s="3" t="s">
         <v>127</v>
       </c>
